--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="293">
   <si>
     <t/>
   </si>
@@ -67,352 +67,580 @@
     <t>5</t>
   </si>
   <si>
+    <t>20052530</t>
+  </si>
+  <si>
+    <t>PLAY DOH MINI 4 PACK</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>20111544</t>
+  </si>
+  <si>
+    <t>WIKI IDM TRK</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>20098313</t>
+  </si>
+  <si>
+    <t>WIKI IDM STORE BRICK</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20133201</t>
+  </si>
+  <si>
+    <t>NRTHLND BRICK SERIES</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>20127783</t>
+  </si>
+  <si>
+    <t>APOLO HEAVY MACHNERY</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20105569</t>
+  </si>
+  <si>
+    <t>EMCO DORAEMON MN FGR</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>20133202</t>
+  </si>
+  <si>
+    <t>NRTHLND DIECAST SERI</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20122578</t>
+  </si>
+  <si>
+    <t>CAT LITTLE MACHINES</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20111543</t>
+  </si>
+  <si>
+    <t>WIKI IDM DLVRY TRUCK</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20124279</t>
+  </si>
+  <si>
+    <t>WIKI BRI DLVRY VHCLE</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20124280</t>
+  </si>
+  <si>
+    <t>WIKI DC IDM  DLVR TR</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20124283</t>
+  </si>
+  <si>
+    <t>WIKI REMOTE CTRL ASS</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20122574</t>
+  </si>
+  <si>
+    <t>H/W MONSTER TRUCK</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20138254</t>
+  </si>
+  <si>
+    <t>JURASIC WORLD FIDGET</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20102474</t>
+  </si>
+  <si>
+    <t>JRSC WORLD SNAP SQAD</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20135143</t>
+  </si>
+  <si>
+    <t>VR TOYS ALIEN SLIME</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20128425</t>
+  </si>
+  <si>
+    <t>WIKI DFRMTN RBOT ASS</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20130556</t>
+  </si>
+  <si>
+    <t>WIKI BOYS SERIES</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>20131019</t>
+  </si>
+  <si>
+    <t>JADA DISNEY FIGURE</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>20132254</t>
+  </si>
+  <si>
+    <t>WIKI IDM UNFRM SRIES</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20140760</t>
+  </si>
+  <si>
+    <t>NT PARKOUR CUTE PET</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20127235</t>
+  </si>
+  <si>
+    <t>QMAN PKMON BRICK ASS</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20134674</t>
+  </si>
+  <si>
+    <t>PLYDH ESSNTL CLR 10S</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>20132056</t>
+  </si>
+  <si>
+    <t>TROLLS BAND TGTHR FG</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>20128423</t>
+  </si>
+  <si>
+    <t>WIKI VRBLE CMBNATION</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20113158</t>
+  </si>
+  <si>
+    <t>EMCO ME&amp;MY CHARMZ</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20140689</t>
+  </si>
+  <si>
+    <t>EMCO SD FLOWER MKR</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20132321</t>
+  </si>
+  <si>
+    <t>VR TOY BLN AIR JMB2S</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20116479</t>
+  </si>
+  <si>
+    <t>SANRIO NECKLACE CHRT</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20131391</t>
+  </si>
+  <si>
+    <t>NRTHLND PLAYSET SERI</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20142945</t>
+  </si>
+  <si>
+    <t>EMCO METALZ PULLBACK</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>TG</t>
+  </si>
+  <si>
+    <t>20113009</t>
+  </si>
+  <si>
+    <t>SM DC SPR.HR FGR ASS</t>
+  </si>
+  <si>
+    <t>20116752</t>
+  </si>
+  <si>
+    <t>BIMA S FGRN 17CM MDR</t>
+  </si>
+  <si>
+    <t>20124284</t>
+  </si>
+  <si>
+    <t>WIKI BUBBLE GUN ASST</t>
+  </si>
+  <si>
+    <t>20135015</t>
+  </si>
+  <si>
+    <t>AMARA STRL MK UP KIT</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140687</t>
+  </si>
+  <si>
+    <t>BARBIE JET TAG JNX28</t>
+  </si>
+  <si>
+    <t>20143374</t>
+  </si>
+  <si>
+    <t>BARBIE SILICON POUCH</t>
+  </si>
+  <si>
+    <t>20143910</t>
+  </si>
+  <si>
+    <t>BARBIE CUTIE KYCHAIN</t>
+  </si>
+  <si>
+    <t>PT,(E-74B)</t>
+  </si>
+  <si>
+    <t>20137817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
+  </si>
+  <si>
+    <t>20095866</t>
+  </si>
+  <si>
+    <t>WIKI GIRL ASST SERI</t>
+  </si>
+  <si>
+    <t>20133754</t>
+  </si>
+  <si>
+    <t>NORTHLAND GIRL SERIE</t>
+  </si>
+  <si>
+    <t>20139049</t>
+  </si>
+  <si>
+    <t>BARBIE CHRM&amp;BRC JML5</t>
+  </si>
+  <si>
+    <t>20133852</t>
+  </si>
+  <si>
+    <t>RHINO SLIME DNT</t>
+  </si>
+  <si>
+    <t>20134161</t>
+  </si>
+  <si>
+    <t>EMCO BLING BANDZ</t>
+  </si>
+  <si>
     <t>20140329</t>
   </si>
   <si>
     <t>BLOKEES HERO INFINTY</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>20052530</t>
-  </si>
-  <si>
-    <t>PLAY DOH MINI 4 PACK</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>20111544</t>
-  </si>
-  <si>
-    <t>WIKI IDM TRK</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20098313</t>
-  </si>
-  <si>
-    <t>WIKI IDM STORE BRICK</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20133201</t>
-  </si>
-  <si>
-    <t>NRTHLND BRICK SERIES</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20105569</t>
-  </si>
-  <si>
-    <t>EMCO DORAEMON MN FGR</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>20133202</t>
-  </si>
-  <si>
-    <t>NRTHLND DIECAST SERI</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20122578</t>
-  </si>
-  <si>
-    <t>CAT LITTLE MACHINES</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20111543</t>
-  </si>
-  <si>
-    <t>WIKI IDM DLVRY TRUCK</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20124279</t>
-  </si>
-  <si>
-    <t>WIKI BRI DLVRY VHCLE</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20124280</t>
-  </si>
-  <si>
-    <t>WIKI DC IDM  DLVR TR</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20124283</t>
-  </si>
-  <si>
-    <t>WIKI REMOTE CTRL ASS</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20122574</t>
-  </si>
-  <si>
-    <t>H/W MONSTER TRUCK</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20138254</t>
-  </si>
-  <si>
-    <t>JURASIC WORLD FIDGET</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20102474</t>
-  </si>
-  <si>
-    <t>JRSC WORLD SNAP SQAD</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20135143</t>
-  </si>
-  <si>
-    <t>VR TOYS ALIEN SLIME</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20128425</t>
-  </si>
-  <si>
-    <t>WIKI DFRMTN RBOT ASS</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20130556</t>
-  </si>
-  <si>
-    <t>WIKI BOYS SERIES</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>20131019</t>
-  </si>
-  <si>
-    <t>JADA DISNEY FIGURE</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>20132254</t>
-  </si>
-  <si>
-    <t>WIKI IDM UNFRM SRIES</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20140760</t>
-  </si>
-  <si>
-    <t>NT PARKOUR CUTE PET</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20127235</t>
-  </si>
-  <si>
-    <t>QMAN PKMON BRICK ASS</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20134674</t>
-  </si>
-  <si>
-    <t>PLYDH ESSNTL CLR 10S</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20138002</t>
-  </si>
-  <si>
-    <t>PIXAR IMPULSE  MINIS</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>20132056</t>
-  </si>
-  <si>
-    <t>TROLLS BAND TGTHR FG</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>20128423</t>
-  </si>
-  <si>
-    <t>WIKI VRBLE CMBNATION</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20113158</t>
-  </si>
-  <si>
-    <t>EMCO ME&amp;MY CHARMZ</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20140689</t>
-  </si>
-  <si>
-    <t>EMCO SD FLOWER MKR</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20132321</t>
-  </si>
-  <si>
-    <t>VR TOY BLN AIR JMB2S</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20116479</t>
-  </si>
-  <si>
-    <t>SANRIO NECKLACE CHRT</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20131391</t>
-  </si>
-  <si>
-    <t>NRTHLND PLAYSET SERI</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20142945</t>
-  </si>
-  <si>
-    <t>EMCO METALZ PULLBACK</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>TG</t>
-  </si>
-  <si>
-    <t>20113009</t>
-  </si>
-  <si>
-    <t>SM DC SPR.HR FGR ASS</t>
-  </si>
-  <si>
-    <t>20116752</t>
-  </si>
-  <si>
-    <t>BIMA S FGRN 17CM MDR</t>
-  </si>
-  <si>
-    <t>20124284</t>
-  </si>
-  <si>
-    <t>WIKI BUBBLE GUN ASST</t>
-  </si>
-  <si>
-    <t>20135015</t>
-  </si>
-  <si>
-    <t>AMARA STRL MK UP KIT</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140687</t>
-  </si>
-  <si>
-    <t>BARBIE JET TAG JNX28</t>
-  </si>
-  <si>
-    <t>20143374</t>
-  </si>
-  <si>
-    <t>BARBIE SILICON POUCH</t>
-  </si>
-  <si>
-    <t>20143910</t>
-  </si>
-  <si>
-    <t>BARBIE CUTIE KYCHAIN</t>
-  </si>
-  <si>
-    <t>PT,(E-74B)</t>
-  </si>
-  <si>
-    <t>20133852</t>
-  </si>
-  <si>
-    <t>RHINO SLIME DNT</t>
+    <t>20132776</t>
+  </si>
+  <si>
+    <t>HW CMPACT CASE HYJ70</t>
+  </si>
+  <si>
+    <t>20124309</t>
+  </si>
+  <si>
+    <t>SM TECH DECK BASIC</t>
+  </si>
+  <si>
+    <t>20123261</t>
+  </si>
+  <si>
+    <t>MTCHBX SKY BST+PLY</t>
+  </si>
+  <si>
+    <t>20007929</t>
+  </si>
+  <si>
+    <t>MATCHBOX MOBIL 30782</t>
+  </si>
+  <si>
+    <t>20111564</t>
+  </si>
+  <si>
+    <t>MTCHBOX MV.PRT FWD28</t>
+  </si>
+  <si>
+    <t>20106824</t>
+  </si>
+  <si>
+    <t>MNSTER JAM VL.TRUCK</t>
+  </si>
+  <si>
+    <t>20123353</t>
+  </si>
+  <si>
+    <t>RKC ROLL SPD METAL</t>
+  </si>
+  <si>
+    <t>10011593</t>
+  </si>
+  <si>
+    <t>HOT WHEELS MBL BASIC</t>
+  </si>
+  <si>
+    <t>20137628</t>
+  </si>
+  <si>
+    <t>HW PEARL&amp;CHROME 2025</t>
+  </si>
+  <si>
+    <t>20137630</t>
+  </si>
+  <si>
+    <t>HW VINTAGE ICON 2025</t>
+  </si>
+  <si>
+    <t>20142563</t>
+  </si>
+  <si>
+    <t>HW AUDI CELEBRATIONS</t>
+  </si>
+  <si>
+    <t>20137629</t>
+  </si>
+  <si>
+    <t>HW SURF UP 2025</t>
+  </si>
+  <si>
+    <t>20142564</t>
+  </si>
+  <si>
+    <t>HW FAST FURIOUS 26</t>
+  </si>
+  <si>
+    <t>20142928</t>
+  </si>
+  <si>
+    <t>HW SILVER FF 2026</t>
+  </si>
+  <si>
+    <t>20133726</t>
+  </si>
+  <si>
+    <t>HW ULTRA HOTS HDG52</t>
+  </si>
+  <si>
+    <t>20140691</t>
+  </si>
+  <si>
+    <t>HW 58TH ANNIV HDH54</t>
+  </si>
+  <si>
+    <t>20142565</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED 2026</t>
+  </si>
+  <si>
+    <t>20007744</t>
+  </si>
+  <si>
+    <t>MOBIL HOT/WL ACL2025</t>
+  </si>
+  <si>
+    <t>20140690</t>
+  </si>
+  <si>
+    <t>HW COMPACT KINGS</t>
+  </si>
+  <si>
+    <t>20140693</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;F 25TH ANNIV</t>
+  </si>
+  <si>
+    <t>20137358</t>
+  </si>
+  <si>
+    <t>HW VINTAGE RCG HRT81</t>
+  </si>
+  <si>
+    <t>20137359</t>
+  </si>
+  <si>
+    <t>HW NEON SPEED HLH72</t>
+  </si>
+  <si>
+    <t>20140692</t>
+  </si>
+  <si>
+    <t>HW LNR NEW YEAR 26</t>
+  </si>
+  <si>
+    <t>20028329</t>
+  </si>
+  <si>
+    <t>H.WHL COLOUR SHIFTER</t>
+  </si>
+  <si>
+    <t>20140694</t>
+  </si>
+  <si>
+    <t>HW THE HOT ONES</t>
+  </si>
+  <si>
+    <t>20140695</t>
+  </si>
+  <si>
+    <t>HW PANTONE JKY47</t>
+  </si>
+  <si>
+    <t>20094698</t>
+  </si>
+  <si>
+    <t>HW MONST.TRUCK FYJ44</t>
+  </si>
+  <si>
+    <t>20144404</t>
+  </si>
+  <si>
+    <t>HW SILVER EXOTICS</t>
+  </si>
+  <si>
+    <t>20136215</t>
+  </si>
+  <si>
+    <t>HW FAST&amp;FR2025 HNR88</t>
+  </si>
+  <si>
+    <t>20137631</t>
+  </si>
+  <si>
+    <t>HW HYBRID SPEED 2025</t>
+  </si>
+  <si>
+    <t>20134458</t>
+  </si>
+  <si>
+    <t>T&amp;F PLSTC ENGINE ASS</t>
+  </si>
+  <si>
+    <t>20136547</t>
+  </si>
+  <si>
+    <t>MNCRAFT MN EGG HXT64</t>
+  </si>
+  <si>
+    <t>20142036</t>
+  </si>
+  <si>
+    <t>TOYS/S SMALL STARS</t>
   </si>
   <si>
     <t>20133723</t>
@@ -421,238 +649,238 @@
     <t>RHINO SWEET LICIOUS</t>
   </si>
   <si>
-    <t>20133754</t>
-  </si>
-  <si>
-    <t>NORTHLAND GIRL SERIE</t>
-  </si>
-  <si>
-    <t>20095866</t>
-  </si>
-  <si>
-    <t>WIKI GIRL ASST SERI</t>
-  </si>
-  <si>
-    <t>20139049</t>
-  </si>
-  <si>
-    <t>BARBIE CHRM&amp;BRC JML5</t>
-  </si>
-  <si>
-    <t>20134161</t>
-  </si>
-  <si>
-    <t>EMCO BLING BANDZ</t>
-  </si>
-  <si>
-    <t>20137817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RHINO NAIL UNICORN  </t>
-  </si>
-  <si>
-    <t>20141254</t>
-  </si>
-  <si>
-    <t>SPNM  GABBYS DLHOUSE</t>
-  </si>
-  <si>
-    <t>20130066</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS ASS</t>
-  </si>
-  <si>
-    <t>20132776</t>
-  </si>
-  <si>
-    <t>HW CMPACT CASE HYJ70</t>
-  </si>
-  <si>
-    <t>20136215</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;FR2025 HNR88</t>
-  </si>
-  <si>
-    <t>20124309</t>
-  </si>
-  <si>
-    <t>SM TECH DECK BASIC</t>
-  </si>
-  <si>
-    <t>20123261</t>
-  </si>
-  <si>
-    <t>MTCHBX SKY BST+PLY</t>
-  </si>
-  <si>
-    <t>20007929</t>
-  </si>
-  <si>
-    <t>MATCHBOX MOBIL 30782</t>
-  </si>
-  <si>
-    <t>20111564</t>
-  </si>
-  <si>
-    <t>MTCHBOX MV.PRT FWD28</t>
-  </si>
-  <si>
-    <t>20106824</t>
-  </si>
-  <si>
-    <t>MNSTER JAM VL.TRUCK</t>
-  </si>
-  <si>
-    <t>20123353</t>
-  </si>
-  <si>
-    <t>RKC ROLL SPD METAL</t>
-  </si>
-  <si>
-    <t>20137630</t>
-  </si>
-  <si>
-    <t>HW VINTAGE ICON 2025</t>
-  </si>
-  <si>
-    <t>10011593</t>
-  </si>
-  <si>
-    <t>HOT WHEELS MBL BASIC</t>
-  </si>
-  <si>
-    <t>20142563</t>
-  </si>
-  <si>
-    <t>HW AUDI CELEBRATIONS</t>
-  </si>
-  <si>
-    <t>20142928</t>
-  </si>
-  <si>
-    <t>HW SILVER FF 2026</t>
-  </si>
-  <si>
-    <t>20142564</t>
-  </si>
-  <si>
-    <t>HW FAST FURIOUS 26</t>
-  </si>
-  <si>
-    <t>20140691</t>
-  </si>
-  <si>
-    <t>HW 58TH ANNIV HDH54</t>
-  </si>
-  <si>
-    <t>20142565</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED 2026</t>
-  </si>
-  <si>
-    <t>20140693</t>
-  </si>
-  <si>
-    <t>HW FAST&amp;F 25TH ANNIV</t>
-  </si>
-  <si>
-    <t>20140690</t>
-  </si>
-  <si>
-    <t>HW COMPACT KINGS</t>
-  </si>
-  <si>
-    <t>20137359</t>
-  </si>
-  <si>
-    <t>HW NEON SPEED HLH72</t>
-  </si>
-  <si>
-    <t>20140692</t>
-  </si>
-  <si>
-    <t>HW LNR NEW YEAR 26</t>
-  </si>
-  <si>
-    <t>20140695</t>
-  </si>
-  <si>
-    <t>HW PANTONE JKY47</t>
-  </si>
-  <si>
-    <t>20028329</t>
-  </si>
-  <si>
-    <t>H.WHL COLOUR SHIFTER</t>
-  </si>
-  <si>
-    <t>20140694</t>
-  </si>
-  <si>
-    <t>HW THE HOT ONES</t>
-  </si>
-  <si>
-    <t>20094698</t>
-  </si>
-  <si>
-    <t>HW MONST.TRUCK FYJ44</t>
-  </si>
-  <si>
-    <t>20137631</t>
-  </si>
-  <si>
-    <t>HW HYBRID SPEED 2025</t>
-  </si>
-  <si>
-    <t>20137628</t>
-  </si>
-  <si>
-    <t>HW PEARL&amp;CHROME 2025</t>
-  </si>
-  <si>
-    <t>20109719</t>
-  </si>
-  <si>
-    <t>HW SHORT BLSTER 2021</t>
-  </si>
-  <si>
-    <t>20137629</t>
-  </si>
-  <si>
-    <t>HW SURF UP 2025</t>
-  </si>
-  <si>
-    <t>20133726</t>
-  </si>
-  <si>
-    <t>HW ULTRA HOTS HDG52</t>
-  </si>
-  <si>
-    <t>20007744</t>
-  </si>
-  <si>
-    <t>MOBIL HOT/WL ACL2025</t>
-  </si>
-  <si>
-    <t>20137358</t>
-  </si>
-  <si>
-    <t>HW VINTAGE RCG HRT81</t>
-  </si>
-  <si>
-    <t>20142036</t>
-  </si>
-  <si>
-    <t>TOYS/S SMALL STARS</t>
-  </si>
-  <si>
-    <t>20134458</t>
-  </si>
-  <si>
-    <t>T&amp;F PLSTC ENGINE ASS</t>
+    <t>20096148</t>
+  </si>
+  <si>
+    <t>WIKI ALPHABET ROBOT</t>
+  </si>
+  <si>
+    <t>20138915</t>
+  </si>
+  <si>
+    <t>APOLO BALON QUU 20G</t>
+  </si>
+  <si>
+    <t>20140422</t>
+  </si>
+  <si>
+    <t>EMCO FUGGLER COLLECT</t>
+  </si>
+  <si>
+    <t>20122573</t>
+  </si>
+  <si>
+    <t>EMCO PAT MYSTERY BOX</t>
+  </si>
+  <si>
+    <t>20133041</t>
+  </si>
+  <si>
+    <t>RHINO CTCH THE MNSTR</t>
+  </si>
+  <si>
+    <t>20140773</t>
+  </si>
+  <si>
+    <t>NT TOOL HOME ENGINR</t>
+  </si>
+  <si>
+    <t>20141538</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX PLUSH</t>
+  </si>
+  <si>
+    <t>RT,(E-24B)</t>
+  </si>
+  <si>
+    <t>20139367</t>
+  </si>
+  <si>
+    <t>ZIGO ULTRAMAN DIY</t>
+  </si>
+  <si>
+    <t>20140767</t>
+  </si>
+  <si>
+    <t>NT SPCL POLICE LIGHT</t>
+  </si>
+  <si>
+    <t>20140777</t>
+  </si>
+  <si>
+    <t>NT PROFESION TOOLS</t>
+  </si>
+  <si>
+    <t>20141539</t>
+  </si>
+  <si>
+    <t>RHINO BLND BOX RESIN</t>
+  </si>
+  <si>
+    <t>20136677</t>
+  </si>
+  <si>
+    <t>EMCO SANRIO CHARACTR</t>
+  </si>
+  <si>
+    <t>20137553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
+  </si>
+  <si>
+    <t>20138913</t>
+  </si>
+  <si>
+    <t>EMCO POCKET TITANS</t>
+  </si>
+  <si>
+    <t>20140756</t>
+  </si>
+  <si>
+    <t>NT SPACE STAR EXPLOR</t>
+  </si>
+  <si>
+    <t>20074122</t>
+  </si>
+  <si>
+    <t>EMCO HOT SHOTS BOLT</t>
+  </si>
+  <si>
+    <t>20140768</t>
+  </si>
+  <si>
+    <t>NT TRAVEL PET HOME</t>
+  </si>
+  <si>
+    <t>20140769</t>
+  </si>
+  <si>
+    <t>NT PLBACK AEROPLANE</t>
+  </si>
+  <si>
+    <t>20142150</t>
+  </si>
+  <si>
+    <t>BLOKEES BATMAN DV</t>
+  </si>
+  <si>
+    <t>20117276</t>
+  </si>
+  <si>
+    <t>HOT WHLS PULL BACK</t>
+  </si>
+  <si>
+    <t>20129931</t>
+  </si>
+  <si>
+    <t>APOLO WOBBLE ASST</t>
+  </si>
+  <si>
+    <t>20133775</t>
+  </si>
+  <si>
+    <t>NORTH DIY ENGNE TRCK</t>
+  </si>
+  <si>
+    <t>20133780</t>
+  </si>
+  <si>
+    <t>NRTHLND TOOL HELPER</t>
+  </si>
+  <si>
+    <t>20092220</t>
+  </si>
+  <si>
+    <t>PLAY DOH VALUE SET</t>
+  </si>
+  <si>
+    <t>20095864</t>
+  </si>
+  <si>
+    <t>WIKI D.CAST REAL CAR</t>
+  </si>
+  <si>
+    <t>20133756</t>
+  </si>
+  <si>
+    <t>NORTH ARMY AIR FORCE</t>
+  </si>
+  <si>
+    <t>20141255</t>
+  </si>
+  <si>
+    <t>BLOKEES TRANSFORMERS</t>
+  </si>
+  <si>
+    <t>20080091</t>
+  </si>
+  <si>
+    <t>APOLO MSZ PULLBACK</t>
+  </si>
+  <si>
+    <t>20134460</t>
+  </si>
+  <si>
+    <t>MEGA PKEMON POKEBALL</t>
+  </si>
+  <si>
+    <t>20140755</t>
+  </si>
+  <si>
+    <t>NT WAR OF TANKS WM</t>
+  </si>
+  <si>
+    <t>20140759</t>
+  </si>
+  <si>
+    <t>NT PUPPY PLAY SET</t>
+  </si>
+  <si>
+    <t>20128424</t>
+  </si>
+  <si>
+    <t>WIKI MNSTER STUN CAR</t>
+  </si>
+  <si>
+    <t>20140757</t>
+  </si>
+  <si>
+    <t>NT A.FG ESCHATOLOGY</t>
+  </si>
+  <si>
+    <t>20142227</t>
+  </si>
+  <si>
+    <t>EMCO POP A TOY NEW S</t>
+  </si>
+  <si>
+    <t>20133771</t>
+  </si>
+  <si>
+    <t>NT HIP HOP BOY FGR</t>
+  </si>
+  <si>
+    <t>20133786</t>
+  </si>
+  <si>
+    <t>NORTH POP UP FR/FROG</t>
+  </si>
+  <si>
+    <t>20140758</t>
+  </si>
+  <si>
+    <t>NT MY LOVELY PET</t>
+  </si>
+  <si>
+    <t>20143747</t>
+  </si>
+  <si>
+    <t>EMCO MYSTERY DMPLG</t>
+  </si>
+  <si>
+    <t>PT,(E-45B)</t>
   </si>
   <si>
     <t>20138914</t>
@@ -661,253 +889,7 @@
     <t>EMCO KIX BRIX</t>
   </si>
   <si>
-    <t>20096148</t>
-  </si>
-  <si>
-    <t>WIKI ALPHABET ROBOT</t>
-  </si>
-  <si>
-    <t>20140422</t>
-  </si>
-  <si>
-    <t>EMCO FUGGLER COLLECT</t>
-  </si>
-  <si>
-    <t>20128424</t>
-  </si>
-  <si>
-    <t>WIKI MNSTER STUN CAR</t>
-  </si>
-  <si>
-    <t>20136547</t>
-  </si>
-  <si>
-    <t>MNCRAFT MN EGG HXT64</t>
-  </si>
-  <si>
-    <t>20138915</t>
-  </si>
-  <si>
-    <t>APOLO BALON QUU 20G</t>
-  </si>
-  <si>
-    <t>20122573</t>
-  </si>
-  <si>
-    <t>EMCO PAT MYSTERY BOX</t>
-  </si>
-  <si>
-    <t>20140755</t>
-  </si>
-  <si>
-    <t>NT WAR OF TANKS WM</t>
-  </si>
-  <si>
-    <t>20140773</t>
-  </si>
-  <si>
-    <t>NT TOOL HOME ENGINR</t>
-  </si>
-  <si>
-    <t>20141538</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX PLUSH</t>
-  </si>
-  <si>
-    <t>RT,(E-24B)</t>
-  </si>
-  <si>
-    <t>20133041</t>
-  </si>
-  <si>
-    <t>RHINO CTCH THE MNSTR</t>
-  </si>
-  <si>
-    <t>20133786</t>
-  </si>
-  <si>
-    <t>NORTH POP UP FR/FROG</t>
-  </si>
-  <si>
-    <t>20139367</t>
-  </si>
-  <si>
-    <t>ZIGO ULTRAMAN DIY</t>
-  </si>
-  <si>
-    <t>RT</t>
-  </si>
-  <si>
-    <t>20140767</t>
-  </si>
-  <si>
-    <t>NT SPCL POLICE LIGHT</t>
-  </si>
-  <si>
-    <t>20140777</t>
-  </si>
-  <si>
-    <t>NT PROFESION TOOLS</t>
-  </si>
-  <si>
-    <t>20141539</t>
-  </si>
-  <si>
-    <t>RHINO BLND BOX RESIN</t>
-  </si>
-  <si>
-    <t>20134460</t>
-  </si>
-  <si>
-    <t>MEGA PKEMON POKEBALL</t>
-  </si>
-  <si>
-    <t>20136677</t>
-  </si>
-  <si>
-    <t>EMCO SANRIO CHARACTR</t>
-  </si>
-  <si>
-    <t>20137553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BLOKEES TRANSFORMER </t>
-  </si>
-  <si>
-    <t>20138913</t>
-  </si>
-  <si>
-    <t>EMCO POCKET TITANS</t>
-  </si>
-  <si>
-    <t>20140756</t>
-  </si>
-  <si>
-    <t>NT SPACE STAR EXPLOR</t>
-  </si>
-  <si>
-    <t>20074122</t>
-  </si>
-  <si>
-    <t>EMCO HOT SHOTS BOLT</t>
-  </si>
-  <si>
-    <t>20092220</t>
-  </si>
-  <si>
-    <t>PLAY DOH VALUE SET</t>
-  </si>
-  <si>
-    <t>20140768</t>
-  </si>
-  <si>
-    <t>NT TRAVEL PET HOME</t>
-  </si>
-  <si>
-    <t>20140769</t>
-  </si>
-  <si>
-    <t>NT PLBACK AEROPLANE</t>
-  </si>
-  <si>
-    <t>20142150</t>
-  </si>
-  <si>
-    <t>BLOKEES BATMAN DV</t>
-  </si>
-  <si>
-    <t>20127783</t>
-  </si>
-  <si>
-    <t>APOLO HEAVY MACHNERY</t>
-  </si>
-  <si>
-    <t>20129931</t>
-  </si>
-  <si>
-    <t>APOLO WOBBLE ASST</t>
-  </si>
-  <si>
-    <t>20133775</t>
-  </si>
-  <si>
-    <t>NORTH DIY ENGNE TRCK</t>
-  </si>
-  <si>
-    <t>20133780</t>
-  </si>
-  <si>
-    <t>NRTHLND TOOL HELPER</t>
-  </si>
-  <si>
-    <t>20143747</t>
-  </si>
-  <si>
-    <t>EMCO MYSTERY DMPLG</t>
-  </si>
-  <si>
-    <t>PT,(E-45B)</t>
-  </si>
-  <si>
-    <t>20117276</t>
-  </si>
-  <si>
-    <t>HOT WHLS PULL BACK</t>
-  </si>
-  <si>
-    <t>20133756</t>
-  </si>
-  <si>
-    <t>NORTH ARMY AIR FORCE</t>
-  </si>
-  <si>
-    <t>20141255</t>
-  </si>
-  <si>
-    <t>BLOKEES TRANSFORMERS</t>
-  </si>
-  <si>
-    <t>20095864</t>
-  </si>
-  <si>
-    <t>WIKI D.CAST REAL CAR</t>
-  </si>
-  <si>
-    <t>20140759</t>
-  </si>
-  <si>
-    <t>NT PUPPY PLAY SET</t>
-  </si>
-  <si>
-    <t>20080091</t>
-  </si>
-  <si>
-    <t>APOLO MSZ PULLBACK</t>
-  </si>
-  <si>
-    <t>20140757</t>
-  </si>
-  <si>
-    <t>NT A.FG ESCHATOLOGY</t>
-  </si>
-  <si>
-    <t>20133771</t>
-  </si>
-  <si>
-    <t>NT HIP HOP BOY FGR</t>
-  </si>
-  <si>
-    <t>20142227</t>
-  </si>
-  <si>
-    <t>EMCO POP A TOY NEW S</t>
-  </si>
-  <si>
-    <t>20140758</t>
-  </si>
-  <si>
-    <t>NT MY LOVELY PET</t>
+    <t>999</t>
   </si>
 </sst>
 </file>
@@ -1300,13 +1282,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
+    <col min="4" max="4" width="5" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
@@ -1528,15 +1510,15 @@
         <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>3</v>
@@ -1545,7 +1527,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -1553,10 +1535,10 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>3</v>
@@ -1565,7 +1547,7 @@
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>5</v>
@@ -1573,10 +1555,10 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
@@ -1585,7 +1567,7 @@
         <v>4</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>5</v>
@@ -1593,10 +1575,10 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
@@ -1605,7 +1587,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>5</v>
@@ -1613,10 +1595,10 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
@@ -1625,7 +1607,7 @@
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>5</v>
@@ -1633,10 +1615,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
@@ -1645,7 +1627,7 @@
         <v>4</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>5</v>
@@ -1653,10 +1635,10 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>3</v>
@@ -1665,7 +1647,7 @@
         <v>4</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>5</v>
@@ -1673,10 +1655,10 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>3</v>
@@ -1685,7 +1667,7 @@
         <v>4</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>5</v>
@@ -1693,10 +1675,10 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
@@ -1705,7 +1687,7 @@
         <v>4</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -1713,10 +1695,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -1725,7 +1707,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>5</v>
@@ -1733,10 +1715,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -1745,7 +1727,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
@@ -1753,10 +1735,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1765,7 +1747,7 @@
         <v>4</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -1773,10 +1755,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1785,7 +1767,7 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>5</v>
@@ -1793,10 +1775,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1805,7 +1787,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1813,10 +1795,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1825,7 +1807,7 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>5</v>
@@ -1833,10 +1815,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1845,18 +1827,18 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1865,7 +1847,7 @@
         <v>4</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>5</v>
@@ -1873,10 +1855,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1885,7 +1867,7 @@
         <v>4</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>5</v>
@@ -1893,10 +1875,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1905,7 +1887,7 @@
         <v>4</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>5</v>
@@ -1913,10 +1895,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1925,7 +1907,7 @@
         <v>4</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>5</v>
@@ -1933,10 +1915,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1945,7 +1927,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1953,10 +1935,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1965,7 +1947,7 @@
         <v>4</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1973,10 +1955,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1985,7 +1967,7 @@
         <v>4</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1993,10 +1975,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -2005,7 +1987,7 @@
         <v>4</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -2013,10 +1995,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -2025,7 +2007,7 @@
         <v>4</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -2033,10 +2015,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -2045,30 +2027,30 @@
         <v>4</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>114</v>
+        <v>4</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>115</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2085,7 +2067,7 @@
         <v>8</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>5</v>
@@ -2105,7 +2087,7 @@
         <v>8</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>5</v>
@@ -2125,18 +2107,18 @@
         <v>8</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2145,10 +2127,10 @@
         <v>8</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>124</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2165,10 +2147,10 @@
         <v>8</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2185,18 +2167,18 @@
         <v>8</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2205,10 +2187,10 @@
         <v>8</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>131</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2325,7 +2307,7 @@
         <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>5</v>
@@ -2342,10 +2324,10 @@
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>5</v>
@@ -2362,10 +2344,10 @@
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>5</v>
@@ -2385,7 +2367,7 @@
         <v>14</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>5</v>
@@ -2405,7 +2387,7 @@
         <v>14</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>5</v>
@@ -2425,7 +2407,7 @@
         <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>5</v>
@@ -2445,7 +2427,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>5</v>
@@ -2465,7 +2447,7 @@
         <v>14</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>5</v>
@@ -2482,10 +2464,10 @@
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>5</v>
@@ -2502,10 +2484,10 @@
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>5</v>
@@ -2522,10 +2504,10 @@
         <v>3</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>5</v>
@@ -2542,13 +2524,13 @@
         <v>3</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2562,10 +2544,10 @@
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>5</v>
@@ -2585,10 +2567,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2608,7 +2590,7 @@
         <v>8</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2645,10 +2627,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2665,10 +2647,10 @@
         <v>17</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2685,10 +2667,10 @@
         <v>17</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2705,7 +2687,7 @@
         <v>17</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>5</v>
@@ -2725,7 +2707,7 @@
         <v>17</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -2745,7 +2727,7 @@
         <v>17</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -2765,7 +2747,7 @@
         <v>17</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -2785,7 +2767,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -2805,7 +2787,7 @@
         <v>17</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>5</v>
@@ -2825,7 +2807,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>5</v>
@@ -2845,7 +2827,7 @@
         <v>17</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>5</v>
@@ -2865,7 +2847,7 @@
         <v>17</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -2885,10 +2867,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>5</v>
+        <v>129</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2905,7 +2887,7 @@
         <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>5</v>
@@ -2925,7 +2907,7 @@
         <v>17</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>5</v>
@@ -2942,10 +2924,10 @@
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2962,10 +2944,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2982,13 +2964,13 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>65</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3005,10 +2987,10 @@
         <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3025,7 +3007,7 @@
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>5</v>
@@ -3045,10 +3027,10 @@
         <v>20</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3065,7 +3047,7 @@
         <v>20</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>5</v>
@@ -3082,10 +3064,10 @@
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>5</v>
@@ -3102,10 +3084,10 @@
         <v>3</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>5</v>
@@ -3122,10 +3104,10 @@
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>5</v>
@@ -3142,21 +3124,21 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>81</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3165,18 +3147,18 @@
         <v>23</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3185,7 +3167,7 @@
         <v>23</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3193,10 +3175,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3205,7 +3187,7 @@
         <v>23</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3213,10 +3195,10 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C96" s="1" t="s">
         <v>3</v>
@@ -3225,10 +3207,10 @@
         <v>23</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3245,7 +3227,7 @@
         <v>23</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3288,15 +3270,15 @@
         <v>11</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>241</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B100" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>243</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>3</v>
@@ -3313,11 +3295,11 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B101" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B101" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
       </c>
@@ -3325,7 +3307,7 @@
         <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3333,11 +3315,11 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B102" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>247</v>
-      </c>
       <c r="C102" s="1" t="s">
         <v>3</v>
       </c>
@@ -3345,18 +3327,18 @@
         <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="B103" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B103" s="1" t="s">
-        <v>249</v>
       </c>
       <c r="C103" s="1" t="s">
         <v>3</v>
@@ -3373,10 +3355,10 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B104" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>251</v>
       </c>
       <c r="C104" s="1" t="s">
         <v>3</v>
@@ -3388,16 +3370,16 @@
         <v>14</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B105" s="1" t="s">
-        <v>253</v>
-      </c>
       <c r="C105" s="1" t="s">
         <v>3</v>
       </c>
@@ -3405,7 +3387,7 @@
         <v>23</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -3413,11 +3395,11 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B106" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B106" s="1" t="s">
-        <v>255</v>
-      </c>
       <c r="C106" s="1" t="s">
         <v>3</v>
       </c>
@@ -3425,19 +3407,19 @@
         <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>81</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="B107" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>257</v>
-      </c>
       <c r="C107" s="1" t="s">
         <v>3</v>
       </c>
@@ -3445,7 +3427,7 @@
         <v>23</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>5</v>
@@ -3453,10 +3435,10 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="B108" s="1" t="s">
-        <v>259</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>3</v>
@@ -3473,11 +3455,11 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B109" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="C109" s="1" t="s">
         <v>3</v>
       </c>
@@ -3485,7 +3467,7 @@
         <v>23</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
@@ -3493,11 +3475,11 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B110" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
       </c>
@@ -3505,7 +3487,7 @@
         <v>23</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>5</v>
@@ -3513,11 +3495,11 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B111" s="1" t="s">
-        <v>265</v>
-      </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
       </c>
@@ -3525,7 +3507,7 @@
         <v>23</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>5</v>
@@ -3533,11 +3515,11 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B112" s="1" t="s">
-        <v>267</v>
-      </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
       </c>
@@ -3545,19 +3527,19 @@
         <v>23</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B113" s="1" t="s">
-        <v>269</v>
-      </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
       </c>
@@ -3565,19 +3547,19 @@
         <v>23</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>241</v>
+        <v>5</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B114" s="1" t="s">
-        <v>271</v>
-      </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
       </c>
@@ -3585,19 +3567,19 @@
         <v>23</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>241</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B115" s="1" t="s">
-        <v>273</v>
-      </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
       </c>
@@ -3605,7 +3587,7 @@
         <v>23</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>5</v>
@@ -3613,11 +3595,11 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B116" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
       </c>
@@ -3625,7 +3607,7 @@
         <v>23</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>5</v>
@@ -3633,11 +3615,11 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B117" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
       </c>
@@ -3645,18 +3627,18 @@
         <v>23</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>278</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -3665,7 +3647,7 @@
         <v>23</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>5</v>
@@ -3673,10 +3655,10 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -3685,18 +3667,18 @@
         <v>23</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C120" s="1" t="s">
         <v>3</v>
@@ -3705,7 +3687,7 @@
         <v>23</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>5</v>
@@ -3713,10 +3695,10 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C121" s="1" t="s">
         <v>3</v>
@@ -3725,7 +3707,7 @@
         <v>23</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>5</v>
@@ -3733,10 +3715,10 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C122" s="1" t="s">
         <v>3</v>
@@ -3745,7 +3727,7 @@
         <v>23</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>5</v>
@@ -3753,102 +3735,42 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F123" s="1" t="s">
         <v>289</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C123" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F123" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B124" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="C124" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C124" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E124" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A125" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="B125" s="1" t="s">
-        <v>294</v>
-      </c>
-      <c r="C125" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F125" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A126" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="B126" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="C126" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A127" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="C127" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F127" s="1" t="s">
-        <v>5</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/TOY01D.xlsx
+++ b/TOY01D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="744" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="295">
   <si>
     <t/>
   </si>
@@ -881,6 +881,12 @@
   </si>
   <si>
     <t>PT,(E-45B)</t>
+  </si>
+  <si>
+    <t>20144451</t>
+  </si>
+  <si>
+    <t>EMCO NEON DOH</t>
   </si>
   <si>
     <t>20138914</t>
@@ -1282,7 +1288,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2310,7 +2316,7 @@
         <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3764,13 +3770,33 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E124" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F124" s="1" t="s">
-        <v>82</v>
+      <c r="B125" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F125" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
   </sheetData>
